--- a/Output/Scanner Summary Matrix_19 Jul 2026.xlsx
+++ b/Output/Scanner Summary Matrix_19 Jul 2026.xlsx
@@ -557,11 +557,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -600,11 +596,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -678,11 +670,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -717,11 +705,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -756,11 +740,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
@@ -799,11 +779,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -838,11 +814,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -885,11 +857,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -928,11 +896,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -967,11 +931,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -1010,11 +970,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -1053,11 +1009,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
@@ -1092,11 +1044,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
@@ -1201,11 +1149,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -1236,11 +1180,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
@@ -1279,11 +1219,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
@@ -1322,11 +1258,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
@@ -1361,11 +1293,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -1400,11 +1328,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
@@ -1439,11 +1363,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
@@ -1486,11 +1406,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
@@ -1525,11 +1441,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
@@ -1564,11 +1476,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
@@ -1607,11 +1515,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
@@ -1642,11 +1546,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
@@ -1685,11 +1585,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
@@ -1724,11 +1620,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
@@ -1763,11 +1655,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
@@ -1806,11 +1694,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
@@ -1919,11 +1803,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
@@ -1958,11 +1838,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -2001,11 +1877,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -2044,11 +1916,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
@@ -2122,11 +1990,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
@@ -2165,11 +2029,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
@@ -2208,11 +2068,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
@@ -2360,11 +2216,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
@@ -2403,11 +2255,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
@@ -2489,11 +2337,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
@@ -2606,11 +2450,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
@@ -2645,11 +2485,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
@@ -2719,11 +2555,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
@@ -2793,11 +2625,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
@@ -2832,11 +2660,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
@@ -2914,11 +2738,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
@@ -2953,11 +2773,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
@@ -3074,11 +2890,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
@@ -3113,11 +2925,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
@@ -3195,11 +3003,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
@@ -3246,11 +3050,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
@@ -3324,11 +3124,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
@@ -3363,11 +3159,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
@@ -3402,11 +3194,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
@@ -3445,11 +3233,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
@@ -3484,11 +3268,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
@@ -3566,11 +3346,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
@@ -3605,11 +3381,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
@@ -3652,11 +3424,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
@@ -3695,11 +3463,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
@@ -3738,11 +3502,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
@@ -3816,11 +3576,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
@@ -3859,11 +3615,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
@@ -3929,11 +3681,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
@@ -3972,11 +3720,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
@@ -4011,11 +3755,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
@@ -4093,11 +3833,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
@@ -4175,11 +3911,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
@@ -4249,11 +3981,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
@@ -4323,11 +4051,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
@@ -4366,11 +4090,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
@@ -4409,11 +4129,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
@@ -4456,11 +4172,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
@@ -4569,11 +4281,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
@@ -4608,11 +4316,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
@@ -4690,11 +4394,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
@@ -4733,11 +4433,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
@@ -4776,11 +4472,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
@@ -4846,11 +4538,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
@@ -4885,11 +4573,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
@@ -5018,11 +4702,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
@@ -5061,11 +4741,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
@@ -5100,11 +4776,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
@@ -5186,11 +4858,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
@@ -5225,11 +4893,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
@@ -5264,11 +4928,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
@@ -5311,11 +4971,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
@@ -5358,11 +5014,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
@@ -5436,11 +5088,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
@@ -5475,11 +5123,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
@@ -5518,11 +5162,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
@@ -5561,11 +5201,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
@@ -5604,11 +5240,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
@@ -5678,11 +5310,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
@@ -5721,11 +5349,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
@@ -5760,11 +5384,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
@@ -5803,11 +5423,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
@@ -5842,11 +5458,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
@@ -5936,11 +5548,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
@@ -6022,11 +5630,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
@@ -6069,11 +5673,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
@@ -6194,11 +5794,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
@@ -6323,11 +5919,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
@@ -6370,11 +5962,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
@@ -6413,11 +6001,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
@@ -6456,11 +6040,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
@@ -6495,11 +6075,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
@@ -6538,11 +6114,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
@@ -6577,11 +6149,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
@@ -6620,11 +6188,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
@@ -6659,11 +6223,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
@@ -6737,11 +6297,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
@@ -6776,11 +6332,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
@@ -6850,11 +6402,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
@@ -6897,11 +6445,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
@@ -6936,11 +6480,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
@@ -6975,11 +6515,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
@@ -7014,11 +6550,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
@@ -7057,11 +6589,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
@@ -7100,11 +6628,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
@@ -7178,11 +6702,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
@@ -7217,11 +6737,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
@@ -7260,11 +6776,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
@@ -7342,11 +6854,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
@@ -7377,11 +6885,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
@@ -7455,11 +6959,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
@@ -7494,11 +6994,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
@@ -7537,11 +7033,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
@@ -7580,11 +7072,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
@@ -7619,11 +7107,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
@@ -7662,11 +7146,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
@@ -7705,11 +7185,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
@@ -7783,11 +7259,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
@@ -7857,11 +7329,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
@@ -7896,11 +7364,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
@@ -7939,11 +7403,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
@@ -8013,11 +7473,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
@@ -8056,11 +7512,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
@@ -8134,11 +7586,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
@@ -8177,11 +7625,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
@@ -8220,11 +7664,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
@@ -8263,11 +7703,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
@@ -8302,11 +7738,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
@@ -8341,11 +7773,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
@@ -8380,11 +7808,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
@@ -8423,11 +7847,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
@@ -8466,11 +7886,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
@@ -8513,11 +7929,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
@@ -8552,11 +7964,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
@@ -8634,11 +8042,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
@@ -8716,11 +8120,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
@@ -8759,11 +8159,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
@@ -8802,11 +8198,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
@@ -8841,11 +8233,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
@@ -8919,11 +8307,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
@@ -8962,11 +8346,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
@@ -9005,11 +8385,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr"/>
@@ -9044,11 +8420,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr"/>
@@ -9161,11 +8533,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr"/>
@@ -9239,11 +8607,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
@@ -10022,11 +9386,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -10743,11 +10103,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -11347,11 +10703,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
@@ -11916,11 +11268,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
@@ -12743,11 +12091,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
@@ -13713,11 +13057,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
@@ -16078,11 +15418,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
@@ -16733,11 +16069,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
@@ -17006,11 +16338,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
@@ -17668,11 +16996,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -18046,11 +17370,7 @@
           <t>RSI &lt; 40</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -20473,11 +19793,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
@@ -20730,11 +20046,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
@@ -21560,11 +20872,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
@@ -21915,11 +21223,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
@@ -23205,11 +22509,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
@@ -23911,11 +23211,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
@@ -25015,11 +24311,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
@@ -25965,11 +25257,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -26600,11 +25888,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
@@ -31622,11 +30906,7 @@
           <t>RSI 40–60</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
@@ -32841,11 +32121,7 @@
           <t>RSI &gt; 60</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
